--- a/data/trans_dic/P34A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P34A_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre</t>
+          <t>Población que no realiza actividad física en su tiempo libre (tasa de respuesta: 99,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,52; 29,74</t>
+          <t>21,4; 29,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,46; 19,18</t>
+          <t>12,3; 19,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,21; 22,99</t>
+          <t>15,21; 23,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,67; 21,76</t>
+          <t>9,08; 22,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,28; 47,24</t>
+          <t>38,3; 47,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,01; 33,58</t>
+          <t>24,79; 33,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,99; 43,33</t>
+          <t>33,63; 43,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,36; 45,02</t>
+          <t>30,02; 44,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,74; 36,77</t>
+          <t>30,66; 36,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,37; 25,29</t>
+          <t>19,52; 25,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,46; 31,73</t>
+          <t>25,16; 31,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,68; 29,37</t>
+          <t>19,71; 29,42</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,82; 40,07</t>
+          <t>32,67; 39,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,85; 22,49</t>
+          <t>16,35; 22,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,11; 30,52</t>
+          <t>23,2; 30,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,16; 41,66</t>
+          <t>29,97; 41,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,52; 48,66</t>
+          <t>40,83; 49,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,8; 31,73</t>
+          <t>24,17; 31,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,78; 40,8</t>
+          <t>33,02; 41,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,69; 39,18</t>
+          <t>19,33; 38,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,67; 42,95</t>
+          <t>37,49; 42,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,16; 25,8</t>
+          <t>21,33; 25,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,06; 34,32</t>
+          <t>29,1; 34,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,99; 38,51</t>
+          <t>25,75; 38,1</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,33; 48,39</t>
+          <t>40,68; 48,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,71; 28,27</t>
+          <t>22,06; 29,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,33; 38,78</t>
+          <t>31,17; 38,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,28; 38,46</t>
+          <t>30,14; 38,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,81; 48,57</t>
+          <t>41,09; 48,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,8; 32,13</t>
+          <t>24,9; 31,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,96; 38,6</t>
+          <t>30,93; 38,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,51; 42,38</t>
+          <t>35,43; 42,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,7; 47,24</t>
+          <t>41,84; 47,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,2; 28,89</t>
+          <t>24,22; 29,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,57; 37,66</t>
+          <t>32,31; 37,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,92; 39,56</t>
+          <t>34,03; 39,29</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>44,71; 53,86</t>
+          <t>45,05; 54,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,43; 28,4</t>
+          <t>21,3; 28,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,46; 42,55</t>
+          <t>34,42; 42,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,72; 36,48</t>
+          <t>11,35; 36,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,57; 48,48</t>
+          <t>39,82; 48,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,6; 32,51</t>
+          <t>24,65; 32,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,4; 42,24</t>
+          <t>34,05; 41,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,51; 48,55</t>
+          <t>34,37; 46,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,6; 49,87</t>
+          <t>43,59; 49,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,2; 29,86</t>
+          <t>24,08; 29,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,75; 41,51</t>
+          <t>35,44; 40,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,25; 38,09</t>
+          <t>18,65; 38,13</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>45,4; 55,59</t>
+          <t>45,97; 55,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,81; 29,65</t>
+          <t>20,96; 29,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,38; 40,55</t>
+          <t>31,4; 40,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35,3; 42,87</t>
+          <t>35,61; 43,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,74; 49,47</t>
+          <t>38,89; 48,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,54; 30,21</t>
+          <t>21,99; 30,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,07; 50,73</t>
+          <t>41,14; 50,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,56; 40,46</t>
+          <t>34,58; 40,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43,45; 50,39</t>
+          <t>43,72; 50,73</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,98; 28,19</t>
+          <t>22,09; 28,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,94; 44,59</t>
+          <t>37,88; 44,45</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,11; 41,09</t>
+          <t>36,1; 40,99</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,29; 44,67</t>
+          <t>33,44; 44,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,66; 26,62</t>
+          <t>16,72; 26,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,05; 43,5</t>
+          <t>33,12; 43,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27,37; 35,17</t>
+          <t>27,63; 35,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43,08; 52,91</t>
+          <t>42,77; 52,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,98; 37,97</t>
+          <t>28,21; 38,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41,04; 51,22</t>
+          <t>40,61; 51,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,24; 38,02</t>
+          <t>10,27; 38,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40,13; 47,82</t>
+          <t>40,09; 47,94</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,05; 31,41</t>
+          <t>24,04; 31,1</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38,42; 45,97</t>
+          <t>38,18; 45,95</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,9; 34,85</t>
+          <t>14,12; 35,0</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>42,74; 56,33</t>
+          <t>41,84; 56,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,1; 34,01</t>
+          <t>22,24; 34,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45,36; 57,01</t>
+          <t>46,26; 56,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37,41; 46,25</t>
+          <t>36,54; 46,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>54,75; 66,14</t>
+          <t>55,08; 66,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,93; 56,22</t>
+          <t>46,35; 56,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,28; 73,92</t>
+          <t>63,03; 73,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>60,0; 66,18</t>
+          <t>59,64; 66,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>52,08; 61,07</t>
+          <t>51,86; 60,91</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37,93; 45,97</t>
+          <t>37,83; 45,7</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57,69; 65,59</t>
+          <t>57,56; 65,67</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51,69; 57,35</t>
+          <t>51,65; 57,38</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>39,54; 42,93</t>
+          <t>39,27; 42,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,05; 24,1</t>
+          <t>21,01; 23,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,17; 35,48</t>
+          <t>32,23; 35,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23,33; 33,88</t>
+          <t>23,82; 34,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44,33; 47,97</t>
+          <t>44,47; 47,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,29; 32,53</t>
+          <t>29,39; 32,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,96; 44,33</t>
+          <t>41,07; 44,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>30,91; 41,08</t>
+          <t>30,79; 41,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42,41; 44,94</t>
+          <t>42,38; 44,89</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25,73; 27,8</t>
+          <t>25,69; 27,86</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37,04; 39,43</t>
+          <t>37,17; 39,57</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,08; 37,09</t>
+          <t>30,06; 36,99</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre</t>
+          <t>Población que no realiza actividad física en su tiempo libre (tasa de respuesta: 99,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>104950; 145063</t>
+          <t>104374; 142640</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56590; 87110</t>
+          <t>55871; 88068</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63806; 96455</t>
+          <t>63806; 97520</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34699; 87040</t>
+          <t>36325; 89716</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>175363; 216381</t>
+          <t>175419; 215828</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>107589; 144493</t>
+          <t>106636; 144979</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>134520; 171488</t>
+          <t>133075; 170393</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>95081; 140997</t>
+          <t>94030; 140381</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>290699; 347765</t>
+          <t>289971; 349226</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>171344; 223636</t>
+          <t>172624; 221343</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>207587; 258701</t>
+          <t>205114; 256251</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>140340; 209471</t>
+          <t>140568; 209794</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>236506; 288727</t>
+          <t>235396; 287438</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>115462; 154147</t>
+          <t>112038; 153984</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>136477; 180207</t>
+          <t>136968; 180016</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>127370; 175965</t>
+          <t>126601; 174915</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>249320; 299388</t>
+          <t>251204; 302986</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>145261; 193610</t>
+          <t>147524; 192243</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>184744; 229920</t>
+          <t>186083; 231965</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>95609; 200430</t>
+          <t>98893; 198489</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>503185; 573780</t>
+          <t>500842; 574341</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>274145; 334308</t>
+          <t>276314; 333950</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>335393; 396076</t>
+          <t>335782; 398049</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>242689; 359634</t>
+          <t>240494; 355830</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>254713; 305643</t>
+          <t>256920; 304952</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>148012; 192783</t>
+          <t>150448; 198667</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>209648; 259455</t>
+          <t>208563; 260756</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>161628; 205310</t>
+          <t>160910; 206461</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>275442; 327845</t>
+          <t>277355; 327870</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>176310; 228362</t>
+          <t>176983; 225796</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>204760; 255291</t>
+          <t>204566; 253480</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>192042; 229244</t>
+          <t>191620; 229542</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>544783; 617290</t>
+          <t>546626; 617582</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>337007; 402375</t>
+          <t>337343; 408844</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>433319; 501111</t>
+          <t>429865; 499539</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>364525; 425124</t>
+          <t>365656; 422258</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>230135; 277212</t>
+          <t>231883; 279050</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>131721; 174571</t>
+          <t>130938; 177044</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>222635; 274902</t>
+          <t>222356; 273021</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>95096; 323526</t>
+          <t>100626; 322173</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>199446; 244384</t>
+          <t>200735; 243793</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>151559; 200317</t>
+          <t>151874; 197279</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>223313; 274177</t>
+          <t>221032; 271466</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>245772; 345735</t>
+          <t>244727; 333416</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>444157; 508028</t>
+          <t>444107; 507711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>297843; 367545</t>
+          <t>296386; 363355</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>462981; 537582</t>
+          <t>459016; 530703</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>291810; 608949</t>
+          <t>298139; 609683</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>172075; 210685</t>
+          <t>174223; 210998</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>89363; 127327</t>
+          <t>90028; 125968</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>149986; 193788</t>
+          <t>150050; 193581</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>197413; 239759</t>
+          <t>199171; 242109</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>154892; 197777</t>
+          <t>155465; 195403</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96448; 135281</t>
+          <t>98465; 135731</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>204046; 252033</t>
+          <t>204399; 252073</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>187822; 219924</t>
+          <t>187947; 221463</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>338404; 392394</t>
+          <t>340476; 395044</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>192829; 247333</t>
+          <t>193762; 250206</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>369823; 434676</t>
+          <t>369256; 433293</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>398190; 453188</t>
+          <t>398135; 451987</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>96241; 129155</t>
+          <t>96667; 129064</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51609; 82461</t>
+          <t>51808; 82841</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>110487; 145439</t>
+          <t>110713; 146706</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100541; 129189</t>
+          <t>101483; 128660</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>145858; 179135</t>
+          <t>144812; 179080</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>99057; 134422</t>
+          <t>99877; 135976</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>155051; 193497</t>
+          <t>153400; 194620</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>62261; 231102</t>
+          <t>62408; 232613</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>251860; 300168</t>
+          <t>251636; 300880</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>159633; 208467</t>
+          <t>159588; 206415</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>273583; 327381</t>
+          <t>271902; 327241</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>116003; 339863</t>
+          <t>137713; 341296</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>89265; 117653</t>
+          <t>87389; 117449</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>55205; 84968</t>
+          <t>55556; 85498</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>116564; 146526</t>
+          <t>118885; 145032</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>105144; 129984</t>
+          <t>102707; 130557</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>179581; 216949</t>
+          <t>180677; 217114</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>178138; 218068</t>
+          <t>179785; 219319</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>253220; 295803</t>
+          <t>252222; 293516</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>254579; 280761</t>
+          <t>253047; 281931</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>279603; 327889</t>
+          <t>278446; 326995</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>241869; 293172</t>
+          <t>241238; 291456</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>379139; 431035</t>
+          <t>378262; 431568</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>364597; 404499</t>
+          <t>364324; 404749</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1277681; 1387470</t>
+          <t>1269057; 1384498</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>720971; 825293</t>
+          <t>719512; 820113</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1091965; 1204174</t>
+          <t>1093989; 1211924</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>804984; 1168999</t>
+          <t>822048; 1173211</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1471330; 1592159</t>
+          <t>1475908; 1591174</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1042002; 1157285</t>
+          <t>1045472; 1157918</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1451762; 1571420</t>
+          <t>1455725; 1574322</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1129133; 1500600</t>
+          <t>1124899; 1504516</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2777688; 2943935</t>
+          <t>2775725; 2940722</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1796791; 1940903</t>
+          <t>1793702; 1945254</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2570329; 2735966</t>
+          <t>2579108; 2745765</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2136716; 2634551</t>
+          <t>2135725; 2627855</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P34A_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,4; 29,25</t>
+          <t>21,44; 29,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,3; 19,39</t>
+          <t>12,63; 19,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,21; 23,25</t>
+          <t>15,33; 23,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,08; 22,43</t>
+          <t>9,43; 20,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,3; 47,12</t>
+          <t>38,49; 47,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,79; 33,7</t>
+          <t>25,23; 34,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,63; 43,06</t>
+          <t>33,3; 43,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,02; 44,82</t>
+          <t>29,58; 43,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,66; 36,92</t>
+          <t>30,69; 36,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,52; 25,03</t>
+          <t>19,62; 25,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,16; 31,43</t>
+          <t>25,13; 31,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,71; 29,42</t>
+          <t>19,99; 29,68</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,67; 39,89</t>
+          <t>32,82; 40,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,35; 22,47</t>
+          <t>16,57; 22,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,2; 30,49</t>
+          <t>23,16; 30,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,97; 41,41</t>
+          <t>28,47; 39,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,83; 49,24</t>
+          <t>40,79; 48,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,17; 31,5</t>
+          <t>24,48; 31,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,02; 41,16</t>
+          <t>33,21; 40,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,33; 38,8</t>
+          <t>33,86; 42,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,49; 42,99</t>
+          <t>37,64; 43,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,33; 25,78</t>
+          <t>21,13; 25,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,1; 34,49</t>
+          <t>28,86; 34,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,75; 38,1</t>
+          <t>32,19; 39,28</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>37,56%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,68; 48,28</t>
+          <t>40,4; 48,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,06; 29,14</t>
+          <t>21,98; 28,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,17; 38,97</t>
+          <t>31,09; 38,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,14; 38,68</t>
+          <t>31,36; 39,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,09; 48,58</t>
+          <t>40,44; 48,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,9; 31,76</t>
+          <t>25,24; 32,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,93; 38,33</t>
+          <t>31,29; 38,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,43; 42,44</t>
+          <t>36,54; 42,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,84; 47,27</t>
+          <t>41,96; 47,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,22; 29,36</t>
+          <t>24,28; 29,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,31; 37,55</t>
+          <t>32,33; 37,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34,03; 39,29</t>
+          <t>34,74; 40,1</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,05; 54,22</t>
+          <t>44,66; 53,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,3; 28,81</t>
+          <t>21,48; 29,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,42; 42,26</t>
+          <t>34,24; 42,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,35; 36,33</t>
+          <t>31,96; 39,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,82; 48,36</t>
+          <t>39,36; 48,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,65; 32,02</t>
+          <t>24,83; 32,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,05; 41,82</t>
+          <t>34,29; 42,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,37; 46,82</t>
+          <t>32,52; 38,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,59; 49,83</t>
+          <t>43,53; 49,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,08; 29,52</t>
+          <t>23,9; 29,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,44; 40,98</t>
+          <t>35,47; 40,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,65; 38,13</t>
+          <t>32,96; 37,64</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>45,97; 55,67</t>
+          <t>45,16; 55,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,96; 29,33</t>
+          <t>20,74; 29,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,4; 40,51</t>
+          <t>30,61; 40,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35,61; 43,29</t>
+          <t>35,75; 43,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,89; 48,87</t>
+          <t>38,69; 48,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,99; 30,31</t>
+          <t>21,22; 29,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,14; 50,73</t>
+          <t>41,51; 50,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,58; 40,75</t>
+          <t>34,41; 40,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43,72; 50,73</t>
+          <t>43,57; 50,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,09; 28,52</t>
+          <t>22,39; 28,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,88; 44,45</t>
+          <t>37,6; 44,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,1; 40,99</t>
+          <t>36,01; 40,91</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,44; 44,64</t>
+          <t>33,3; 44,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,72; 26,74</t>
+          <t>17,05; 26,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,12; 43,88</t>
+          <t>32,41; 43,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27,63; 35,03</t>
+          <t>27,77; 35,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42,77; 52,9</t>
+          <t>43,26; 52,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,21; 38,41</t>
+          <t>27,96; 38,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,61; 51,52</t>
+          <t>41,1; 51,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,27; 38,27</t>
+          <t>33,86; 40,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40,09; 47,94</t>
+          <t>40,25; 47,46</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,04; 31,1</t>
+          <t>24,07; 31,21</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38,18; 45,95</t>
+          <t>38,58; 45,7</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,12; 35,0</t>
+          <t>31,54; 36,71</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,35%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,84; 56,24</t>
+          <t>42,39; 55,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,24; 34,22</t>
+          <t>22,08; 33,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46,26; 56,43</t>
+          <t>45,49; 56,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36,54; 46,45</t>
+          <t>36,52; 45,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>55,08; 66,19</t>
+          <t>55,24; 66,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,35; 56,54</t>
+          <t>45,99; 56,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,03; 73,35</t>
+          <t>62,7; 73,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>59,64; 66,45</t>
+          <t>60,05; 66,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51,86; 60,91</t>
+          <t>52,31; 61,21</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37,83; 45,7</t>
+          <t>37,32; 45,82</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57,56; 65,67</t>
+          <t>57,75; 65,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51,65; 57,38</t>
+          <t>51,66; 57,34</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>39,27; 42,84</t>
+          <t>39,18; 42,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,01; 23,94</t>
+          <t>21,01; 23,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,23; 35,7</t>
+          <t>32,19; 35,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23,82; 34,0</t>
+          <t>31,71; 35,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44,47; 47,94</t>
+          <t>44,36; 47,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,39; 32,55</t>
+          <t>29,27; 32,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,07; 44,42</t>
+          <t>41,15; 44,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>30,79; 41,18</t>
+          <t>39,14; 41,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42,38; 44,89</t>
+          <t>42,42; 44,95</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25,69; 27,86</t>
+          <t>25,74; 27,83</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37,17; 39,57</t>
+          <t>37,31; 39,61</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,06; 36,99</t>
+          <t>36,01; 38,11</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57763</t>
+          <t>56599</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>115072</t>
+          <t>132379</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>172835</t>
+          <t>188979</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>104374; 142640</t>
+          <t>104558; 145717</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55871; 88068</t>
+          <t>57354; 88923</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63806; 97520</t>
+          <t>64306; 96577</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36325; 89716</t>
+          <t>38442; 85072</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>175419; 215828</t>
+          <t>176288; 216673</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>106636; 144979</t>
+          <t>108567; 147256</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>133075; 170393</t>
+          <t>131769; 170275</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>94030; 140381</t>
+          <t>107227; 158151</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289971; 349226</t>
+          <t>290270; 345303</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>172624; 221343</t>
+          <t>173475; 223138</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>205114; 256251</t>
+          <t>204902; 258609</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>140568; 209794</t>
+          <t>154008; 228649</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149562</t>
+          <t>158817</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>165802</t>
+          <t>190628</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>315363</t>
+          <t>349446</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>235396; 287438</t>
+          <t>236511; 289795</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>112038; 153984</t>
+          <t>113589; 153976</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>136968; 180016</t>
+          <t>136737; 181181</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>126601; 174915</t>
+          <t>135399; 186538</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>251204; 302986</t>
+          <t>251009; 301035</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>147524; 192243</t>
+          <t>149369; 194601</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>186083; 231965</t>
+          <t>187161; 230280</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>98893; 198489</t>
+          <t>169681; 214146</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>500842; 574341</t>
+          <t>502809; 579325</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>276314; 333950</t>
+          <t>273818; 335978</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>335782; 398049</t>
+          <t>333004; 396289</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>240494; 355830</t>
+          <t>314417; 383665</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>183535</t>
+          <t>219323</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>210475</t>
+          <t>245717</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>394010</t>
+          <t>465039</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>256920; 304952</t>
+          <t>255190; 304731</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>150448; 198667</t>
+          <t>149848; 195200</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>208563; 260756</t>
+          <t>208038; 259865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>160910; 206461</t>
+          <t>193875; 246435</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>277355; 327870</t>
+          <t>272959; 326425</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>176983; 225796</t>
+          <t>179428; 228587</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>204566; 253480</t>
+          <t>206968; 254050</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>191620; 229542</t>
+          <t>226492; 266442</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>546626; 617582</t>
+          <t>548222; 620589</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>337343; 408844</t>
+          <t>338120; 404442</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>429865; 499539</t>
+          <t>430202; 497248</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>365656; 422258</t>
+          <t>430118; 496516</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>224352</t>
+          <t>248916</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>274506</t>
+          <t>258316</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>498858</t>
+          <t>507232</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>231883; 279050</t>
+          <t>229850; 277072</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>130938; 177044</t>
+          <t>132033; 179419</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>222356; 273021</t>
+          <t>221197; 273260</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>100626; 322173</t>
+          <t>223554; 275149</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>200735; 243793</t>
+          <t>198427; 244090</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>151874; 197279</t>
+          <t>153004; 201277</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>221032; 271466</t>
+          <t>222596; 273747</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>244727; 333416</t>
+          <t>239367; 280487</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>444107; 507711</t>
+          <t>443467; 508727</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>296386; 363355</t>
+          <t>294134; 361497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>459016; 530703</t>
+          <t>459397; 530861</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>298139; 609683</t>
+          <t>473234; 540292</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>219753</t>
+          <t>239947</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>204671</t>
+          <t>226651</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>424424</t>
+          <t>466598</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>174223; 210998</t>
+          <t>171140; 210719</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>90028; 125968</t>
+          <t>89070; 125851</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>150050; 193581</t>
+          <t>146282; 193090</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>199171; 242109</t>
+          <t>217145; 264522</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>155465; 195403</t>
+          <t>154701; 194667</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98465; 135731</t>
+          <t>95028; 132927</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>204399; 252073</t>
+          <t>206266; 252640</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>187947; 221463</t>
+          <t>208279; 245861</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>340476; 395044</t>
+          <t>339329; 394878</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>193762; 250206</t>
+          <t>196422; 251220</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>369256; 433293</t>
+          <t>366502; 432269</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>398135; 451987</t>
+          <t>436727; 496128</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>114569</t>
+          <t>127471</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>148857</t>
+          <t>163446</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>263426</t>
+          <t>290918</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>96667; 129064</t>
+          <t>96286; 128228</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51808; 82841</t>
+          <t>52816; 82793</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>110713; 146706</t>
+          <t>108360; 145335</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>101483; 128660</t>
+          <t>112764; 143339</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>144812; 179080</t>
+          <t>146458; 179141</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>99877; 135976</t>
+          <t>98961; 135407</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>153400; 194620</t>
+          <t>155257; 192777</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>62408; 232613</t>
+          <t>148479; 179247</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>251636; 300880</t>
+          <t>252618; 297903</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>159588; 206415</t>
+          <t>159749; 207135</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>271902; 327241</t>
+          <t>274740; 325430</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>137713; 341296</t>
+          <t>266413; 310049</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>116568</t>
+          <t>127230</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>267629</t>
+          <t>291693</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>384196</t>
+          <t>418924</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>87389; 117449</t>
+          <t>88526; 116750</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>55556; 85498</t>
+          <t>55173; 84294</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118885; 145032</t>
+          <t>116907; 146271</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>102707; 130557</t>
+          <t>112558; 141273</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>180677; 217114</t>
+          <t>181195; 219500</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>179785; 219319</t>
+          <t>178367; 220764</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>252222; 293516</t>
+          <t>250902; 294036</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>253047; 281931</t>
+          <t>277790; 308102</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>278446; 326995</t>
+          <t>280829; 328599</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>241238; 291456</t>
+          <t>237989; 292215</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>378262; 431568</t>
+          <t>379521; 431269</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>364324; 404749</t>
+          <t>398171; 441985</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1066102</t>
+          <t>1178305</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1387012</t>
+          <t>1508830</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2453114</t>
+          <t>2687135</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1269057; 1384498</t>
+          <t>1266243; 1378935</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>719512; 820113</t>
+          <t>719529; 818528</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1093989; 1211924</t>
+          <t>1092772; 1209112</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>822048; 1173211</t>
+          <t>1117217; 1240274</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1475908; 1591174</t>
+          <t>1472231; 1591192</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1045472; 1157918</t>
+          <t>1041111; 1153592</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1455725; 1574322</t>
+          <t>1458520; 1578005</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1124899; 1504516</t>
+          <t>1458472; 1558289</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2775725; 2940722</t>
+          <t>2778487; 2944256</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1793702; 1945254</t>
+          <t>1797037; 1943348</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2579108; 2745765</t>
+          <t>2589110; 2748514</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2135725; 2627855</t>
+          <t>2610556; 2762835</t>
         </is>
       </c>
     </row>
